--- a/Speciallægeloft/speciallægeloft_data/Region_Nordjylland.xlsx
+++ b/Speciallægeloft/speciallægeloft_data/Region_Nordjylland.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="50">
   <si>
     <t xml:space="preserve">Antal ansatte - 002 - </t>
   </si>
@@ -19,42 +19,42 @@
     <t/>
   </si>
   <si>
+    <t>dec 2024</t>
+  </si>
+  <si>
+    <t>jan 2025</t>
+  </si>
+  <si>
+    <t>feb 2025</t>
+  </si>
+  <si>
+    <t>mar 2025</t>
+  </si>
+  <si>
+    <t>apr 2025</t>
+  </si>
+  <si>
+    <t>maj 2025</t>
+  </si>
+  <si>
+    <t>jun 2025</t>
+  </si>
+  <si>
+    <t>jul 2025</t>
+  </si>
+  <si>
+    <t>aug 2025</t>
+  </si>
+  <si>
+    <t>sep 2025</t>
+  </si>
+  <si>
+    <t>okt 2025</t>
+  </si>
+  <si>
     <t>nov 2025</t>
   </si>
   <si>
-    <t>okt 2025</t>
-  </si>
-  <si>
-    <t>sep 2025</t>
-  </si>
-  <si>
-    <t>aug 2025</t>
-  </si>
-  <si>
-    <t>jul 2025</t>
-  </si>
-  <si>
-    <t>jun 2025</t>
-  </si>
-  <si>
-    <t>maj 2025</t>
-  </si>
-  <si>
-    <t>apr 2025</t>
-  </si>
-  <si>
-    <t>mar 2025</t>
-  </si>
-  <si>
-    <t>feb 2025</t>
-  </si>
-  <si>
-    <t>jan 2025</t>
-  </si>
-  <si>
-    <t>dec 2024</t>
-  </si>
-  <si>
     <t>Organisation niveau 1</t>
   </si>
   <si>
@@ -79,10 +79,10 @@
     <t>Lokale Løndata</t>
   </si>
   <si>
-    <t>Datasæt 11 2025</t>
-  </si>
-  <si>
-    <t>Kørsel 15.4.2026 13.37.20</t>
+    <t>Datasæt 12 2024</t>
+  </si>
+  <si>
+    <t>Kørsel 15.4.2026 14.35.16</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
@@ -149,6 +149,18 @@
   </si>
   <si>
     <t>1 Månedslønede (bagud)</t>
+  </si>
+  <si>
+    <t>Kontoplan (Aktuel struktur)</t>
+  </si>
+  <si>
+    <t>4 Fællesformål og administration</t>
+  </si>
+  <si>
+    <t>11001 Somatiske sygehuse</t>
+  </si>
+  <si>
+    <t>15034 Decentral adm sundhedsomr ex psykiatri</t>
   </si>
 </sst>
 </file>
@@ -594,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -705,19 +717,19 @@
         <v>16</v>
       </c>
       <c r="B4" s="6">
+        <v>175</v>
+      </c>
+      <c r="C4" s="6">
         <v>178</v>
       </c>
-      <c r="C4" s="6">
+      <c r="D4" s="6">
         <v>179</v>
       </c>
-      <c r="D4" s="6">
-        <v>175</v>
-      </c>
       <c r="E4" s="6">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F4" s="6">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G4" s="6">
         <v>181</v>
@@ -726,19 +738,19 @@
         <v>181</v>
       </c>
       <c r="I4" s="6">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J4" s="6">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K4" s="6">
+        <v>175</v>
+      </c>
+      <c r="L4" s="6">
         <v>179</v>
       </c>
-      <c r="L4" s="6">
+      <c r="M4" s="6">
         <v>178</v>
-      </c>
-      <c r="M4" s="6">
-        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -746,40 +758,40 @@
         <v>17</v>
       </c>
       <c r="B5" s="8">
+        <v>34</v>
+      </c>
+      <c r="C5" s="8">
+        <v>40</v>
+      </c>
+      <c r="D5" s="8">
+        <v>39</v>
+      </c>
+      <c r="E5" s="8">
+        <v>39</v>
+      </c>
+      <c r="F5" s="8">
+        <v>37</v>
+      </c>
+      <c r="G5" s="8">
         <v>38</v>
       </c>
-      <c r="C5" s="8">
+      <c r="H5" s="8">
+        <v>37</v>
+      </c>
+      <c r="I5" s="8">
         <v>38</v>
       </c>
-      <c r="D5" s="8">
+      <c r="J5" s="8">
+        <v>37</v>
+      </c>
+      <c r="K5" s="8">
         <v>36</v>
       </c>
-      <c r="E5" s="8">
-        <v>37</v>
-      </c>
-      <c r="F5" s="8">
+      <c r="L5" s="8">
         <v>38</v>
       </c>
-      <c r="G5" s="8">
-        <v>37</v>
-      </c>
-      <c r="H5" s="8">
+      <c r="M5" s="8">
         <v>38</v>
-      </c>
-      <c r="I5" s="8">
-        <v>37</v>
-      </c>
-      <c r="J5" s="8">
-        <v>39</v>
-      </c>
-      <c r="K5" s="8">
-        <v>39</v>
-      </c>
-      <c r="L5" s="8">
-        <v>40</v>
-      </c>
-      <c r="M5" s="8">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -787,40 +799,40 @@
         <v>18</v>
       </c>
       <c r="B6" s="6">
+        <v>139</v>
+      </c>
+      <c r="C6" s="6">
+        <v>136</v>
+      </c>
+      <c r="D6" s="6">
         <v>138</v>
       </c>
-      <c r="C6" s="6">
+      <c r="E6" s="6">
+        <v>141</v>
+      </c>
+      <c r="F6" s="6">
+        <v>142</v>
+      </c>
+      <c r="G6" s="6">
+        <v>141</v>
+      </c>
+      <c r="H6" s="6">
+        <v>142</v>
+      </c>
+      <c r="I6" s="6">
+        <v>138</v>
+      </c>
+      <c r="J6" s="6">
+        <v>140</v>
+      </c>
+      <c r="K6" s="6">
+        <v>137</v>
+      </c>
+      <c r="L6" s="6">
         <v>139</v>
       </c>
-      <c r="D6" s="6">
-        <v>137</v>
-      </c>
-      <c r="E6" s="6">
-        <v>140</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="M6" s="6">
         <v>138</v>
-      </c>
-      <c r="G6" s="6">
-        <v>142</v>
-      </c>
-      <c r="H6" s="6">
-        <v>141</v>
-      </c>
-      <c r="I6" s="6">
-        <v>142</v>
-      </c>
-      <c r="J6" s="6">
-        <v>141</v>
-      </c>
-      <c r="K6" s="6">
-        <v>138</v>
-      </c>
-      <c r="L6" s="6">
-        <v>136</v>
-      </c>
-      <c r="M6" s="6">
-        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1041,6 +1053,30 @@
       </c>
       <c r="B43" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B47" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
